--- a/wakayama_traffic_map/御坊署_多発交差点一覧_R3-R7.xlsx
+++ b/wakayama_traffic_map/御坊署_多発交差点一覧_R3-R7.xlsx
@@ -612,10 +612,10 @@
         <v>9</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>33.8995</v>
+        <v>33.897904</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>135.1582</v>
+        <v>135.149983</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
@@ -673,10 +673,10 @@
         <v>7</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>33.905</v>
+        <v>33.90455</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>135.1576</v>
+        <v>135.150511</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         <v>7</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>33.8973</v>
+        <v>33.897095</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>135.1452</v>
+        <v>135.144597</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
         <v>6</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>33.9088</v>
+        <v>33.910379</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>135.1756</v>
+        <v>135.174564</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
@@ -1072,10 +1072,10 @@
         <v>10</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>33.8961</v>
+        <v>33.895568</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>135.1576</v>
+        <v>135.157305</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -1125,10 +1125,10 @@
         <v>9</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>33.8983</v>
+        <v>33.898973</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>135.1534</v>
+        <v>135.153921</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -1178,10 +1178,10 @@
         <v>7</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>33.8911</v>
+        <v>33.89071</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>135.1557</v>
+        <v>135.156784</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -1231,14 +1231,14 @@
         <v>6</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>33.8978</v>
+        <v>33.89707</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>135.1582</v>
+        <v>135.150242</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>確度高</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr"/>
@@ -1574,10 +1574,10 @@
         <v>5</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>33.8812</v>
+        <v>33.881175</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>135.1593</v>
+        <v>135.157975</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>

--- a/wakayama_traffic_map/御坊署_多発交差点一覧_R3-R7.xlsx
+++ b/wakayama_traffic_map/御坊署_多発交差点一覧_R3-R7.xlsx
@@ -734,14 +734,14 @@
         <v>7</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>33.9022</v>
+        <v>33.902158</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>135.156</v>
+        <v>135.161556</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>確度高</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr"/>
@@ -852,14 +852,14 @@
         <v>9</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>33.886</v>
+        <v>33.886809</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>135.1585</v>
+        <v>135.152412</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>確度高</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr"/>
@@ -909,14 +909,14 @@
         <v>8</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>33.938</v>
+        <v>33.954899</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>135.129</v>
+        <v>135.122554</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>確度高</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr"/>
@@ -1019,10 +1019,10 @@
         <v>11</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>33.9072</v>
+        <v>33.906958</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>135.1586</v>
+        <v>135.159675</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
@@ -1378,14 +1378,14 @@
         <v>6</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>33.89</v>
+        <v>33.893768</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>135.1583</v>
+        <v>135.151208</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>確度高</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr"/>
@@ -1525,14 +1525,14 @@
         <v>5</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>33.8936</v>
+        <v>33.891437</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>135.1634</v>
+        <v>135.162252</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>確度高</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr"/>

--- a/wakayama_traffic_map/御坊署_多発交差点一覧_R3-R7.xlsx
+++ b/wakayama_traffic_map/御坊署_多発交差点一覧_R3-R7.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1280,10 +1280,10 @@
         <v>7</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>33.8924</v>
+        <v>33.891548</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>135.1528</v>
+        <v>135.151706</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1329,14 +1329,14 @@
         <v>6</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>33.8912</v>
+        <v>33.894498</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>135.1636</v>
+        <v>135.162174</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>確度高</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr"/>
@@ -1427,14 +1427,14 @@
         <v>6</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>33.9004</v>
+        <v>33.901149</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>135.173</v>
+        <v>135.171272</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>確度高</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr"/>
@@ -1476,14 +1476,14 @@
         <v>6</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>33.9005</v>
+        <v>33.918354</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>135.17</v>
+        <v>135.164617</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>確度高</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr"/>
@@ -1623,19 +1623,68 @@
         <v>5</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>33.895</v>
+        <v>33.894905</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>135.1555</v>
+        <v>135.155174</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>確度高</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr"/>
       <c r="P21" s="3" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>斎橋南</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>御坊市</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>県道井関御坊線</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>8位/5件</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>33.904872</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>135.151902</v>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>確度高</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr"/>
+      <c r="P22" s="3" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
